--- a/outputs/2026-01-30/quality_by_entity.xlsx
+++ b/outputs/2026-01-30/quality_by_entity.xlsx
@@ -493,13 +493,13 @@
         <v>8097</v>
       </c>
       <c r="D2" t="n">
-        <v>16400</v>
+        <v>16395</v>
       </c>
       <c r="E2" t="n">
         <v>5727</v>
       </c>
       <c r="F2" t="n">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="G2" t="n">
         <v>25.35</v>
@@ -867,13 +867,13 @@
         <v>4616</v>
       </c>
       <c r="D13" t="n">
-        <v>5188</v>
+        <v>5187</v>
       </c>
       <c r="E13" t="n">
         <v>597</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>44.37</v>
@@ -901,13 +901,13 @@
         <v>4382</v>
       </c>
       <c r="D14" t="n">
-        <v>7724</v>
+        <v>7697</v>
       </c>
       <c r="E14" t="n">
         <v>7063</v>
       </c>
       <c r="F14" t="n">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="G14" t="n">
         <v>21.24</v>
@@ -935,13 +935,13 @@
         <v>3386</v>
       </c>
       <c r="D15" t="n">
-        <v>7031</v>
+        <v>7012</v>
       </c>
       <c r="E15" t="n">
         <v>4834</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
         <v>22.15</v>
